--- a/sources/king_step4.xlsx
+++ b/sources/king_step4.xlsx
@@ -1047,6 +1047,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1084,6 +1089,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1121,6 +1131,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1158,6 +1173,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1205,6 +1225,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1237,6 +1262,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1274,6 +1304,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1311,6 +1346,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -1348,6 +1388,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -1385,6 +1430,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -1422,6 +1472,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -1459,6 +1514,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -1496,6 +1556,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -1533,6 +1598,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -1580,6 +1650,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -1612,6 +1687,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -1649,6 +1729,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -1696,6 +1781,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -1738,6 +1828,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -1780,6 +1875,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -1817,6 +1917,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -1852,6 +1957,11 @@
       <c r="L35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -1996,6 +2106,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -2038,6 +2153,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -2075,6 +2195,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -2112,6 +2237,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -2149,6 +2279,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -2191,6 +2326,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -2233,6 +2373,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -2275,6 +2420,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -2317,6 +2467,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -2357,6 +2512,11 @@
       <c r="L48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6393,6 +6553,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -6425,6 +6590,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -6462,6 +6632,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -6499,6 +6674,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -6536,6 +6716,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -6583,6 +6768,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -6620,6 +6810,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -6657,6 +6852,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -6699,6 +6899,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -6731,6 +6936,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -6768,6 +6978,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -6805,6 +7020,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -6842,6 +7062,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -6879,6 +7104,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -6916,6 +7146,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -6968,6 +7203,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -7005,6 +7245,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -7042,6 +7287,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -7079,6 +7329,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -7116,6 +7371,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -7153,6 +7413,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -7190,6 +7455,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -7227,6 +7497,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -7264,6 +7539,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -7301,6 +7581,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -7338,6 +7623,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -7375,6 +7665,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -7412,6 +7707,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -7449,6 +7749,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -7491,6 +7796,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -7533,6 +7843,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -7570,6 +7885,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -7602,6 +7922,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -7639,6 +7964,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -7676,6 +8006,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -7713,6 +8048,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -7750,6 +8090,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -7787,6 +8132,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -7824,6 +8174,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -7859,6 +8214,11 @@
       <c r="L171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -7993,6 +8353,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -8020,6 +8385,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -8047,6 +8417,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -8074,6 +8449,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -8101,6 +8481,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -8128,6 +8513,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -8155,6 +8545,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -8182,6 +8577,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -8209,6 +8609,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -8234,6 +8639,11 @@
       <c r="J184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">

--- a/sources/king_step4.xlsx
+++ b/sources/king_step4.xlsx
@@ -1247,6 +1247,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1289,6 +1294,11 @@
           <t>– 2,1,2,1,2</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1329,6 +1339,11 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>– 1,2,1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
